--- a/data/Original_data/3_Effects directions of 55 indicators.xlsx
+++ b/data/Original_data/3_Effects directions of 55 indicators.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uflorida-my.sharepoint.com/personal/genhong_gao_ufl_edu/Documents/Documents/PhD/PhD Programs/SDG/2_cities SDGs 082024/Statistical Analysis/Final_Data_082025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_F25DC773A252ABDACC104864E1DC7A805BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C52264CE-789C-40E5-A105-45239DCBCAD7}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="11_F25DC773A252ABDACC104864E1DC7A805BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B5C991B-EE14-4B79-ADE3-D987F4100C09}"/>
   <bookViews>
-    <workbookView xWindow="3180" yWindow="1560" windowWidth="21012" windowHeight="11316" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2160" yWindow="2688" windowWidth="22416" windowHeight="9024" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -231,8 +231,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -519,9 +520,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B56"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="1"/>
+    <col min="3" max="4" width="10.77734375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -529,7 +534,7 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2">
@@ -537,7 +542,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B3">
@@ -545,7 +550,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B4">
@@ -553,7 +558,7 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B5">
@@ -561,7 +566,7 @@
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B6">
@@ -569,7 +574,7 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B7">
@@ -577,7 +582,7 @@
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B8">
@@ -585,7 +590,7 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B9">
@@ -593,7 +598,7 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B10">
@@ -601,7 +606,7 @@
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B11">
@@ -609,7 +614,7 @@
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B12">
@@ -617,7 +622,7 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B13">
@@ -625,7 +630,7 @@
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B14">
@@ -633,7 +638,7 @@
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B15">
@@ -641,7 +646,7 @@
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B16">
@@ -649,7 +654,7 @@
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B17">
@@ -657,7 +662,7 @@
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B18">
@@ -665,7 +670,7 @@
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B19">
@@ -673,7 +678,7 @@
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="A20" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B20">
@@ -681,15 +686,15 @@
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="A21" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="A22" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B22">
@@ -697,7 +702,7 @@
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="A23" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B23">
@@ -705,7 +710,7 @@
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B24">
@@ -713,7 +718,7 @@
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B25">
@@ -721,7 +726,7 @@
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B26">
@@ -729,7 +734,7 @@
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B27">
@@ -737,7 +742,7 @@
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B28">
@@ -745,7 +750,7 @@
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B29">
@@ -753,7 +758,7 @@
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="A30" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B30">
@@ -761,7 +766,7 @@
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="A31" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B31">
@@ -769,7 +774,7 @@
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="A32" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B32">
@@ -777,7 +782,7 @@
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="A33" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B33">
@@ -785,7 +790,7 @@
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="A34" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B34">
@@ -793,7 +798,7 @@
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="A35" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B35">
@@ -801,7 +806,7 @@
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+      <c r="A36" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B36">
@@ -809,7 +814,7 @@
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B37">
@@ -817,15 +822,15 @@
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+      <c r="A38" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B38">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+      <c r="A39" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B39">
@@ -833,7 +838,7 @@
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="A40" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B40">
@@ -841,7 +846,7 @@
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+      <c r="A41" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B41">
@@ -849,7 +854,7 @@
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+      <c r="A42" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B42">
@@ -857,7 +862,7 @@
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+      <c r="A43" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B43">
@@ -865,7 +870,7 @@
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+      <c r="A44" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B44">
@@ -873,7 +878,7 @@
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+      <c r="A45" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B45">
@@ -881,7 +886,7 @@
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+      <c r="A46" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B46">
@@ -889,7 +894,7 @@
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+      <c r="A47" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B47">
@@ -897,7 +902,7 @@
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+      <c r="A48" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B48">
@@ -905,7 +910,7 @@
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+      <c r="A49" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B49">
@@ -913,7 +918,7 @@
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+      <c r="A50" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B50">
@@ -921,7 +926,7 @@
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+      <c r="A51" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B51">
@@ -929,7 +934,7 @@
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+      <c r="A52" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B52">
@@ -937,7 +942,7 @@
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+      <c r="A53" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B53">
@@ -945,7 +950,7 @@
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+      <c r="A54" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B54">
@@ -953,7 +958,7 @@
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+      <c r="A55" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B55">
@@ -961,7 +966,7 @@
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+      <c r="A56" s="1" t="s">
         <v>55</v>
       </c>
       <c r="B56">
